--- a/output/pms/Lập_trình_Python/Session 04 - Toán tử số học, logic và Cấu trúc rẽ nhánh/Lesson 04 - Cấu trúc rẽ nhánh lồng nhau và Chuẩn hóa mã nguồn PEP 8/Câu hỏi Quizz/Quizz_Session04_Lesson04.xlsx
+++ b/output/pms/Lập_trình_Python/Session 04 - Toán tử số học, logic và Cấu trúc rẽ nhánh/Lesson 04 - Cấu trúc rẽ nhánh lồng nhau và Chuẩn hóa mã nguồn PEP 8/Câu hỏi Quizz/Quizz_Session04_Lesson04.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Quy trình thẩm định tín dụng tự động yêu cầu hồ sơ đáp ứng cả 3 tiêu chí: độ tuổi từ 18 đến 65, thu nhập tối thiểu 15 triệu VNĐ và điểm tín dụng đạt từ 650 điểm. Đoạn mã Python nào dưới đây thể hiện cách viết phẳng hóa điều kiện chính xác và tuân thủ PEP 8?</t>
+          <t>Trong hệ thống thẩm định khoản vay tự động của RikkeiBank, lập trình viên cần viết cấu trúc rẽ nhánh lồng nhau (`if` lồng nhau) để kiểm tra hồ sơ khách hàng. Theo quy chuẩn trình bày mã nguồn PEP 8 của Python, quy định bắt buộc nào sau đây phải được tuân thủ về mặt thụt lề (indentation)?</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -491,10 +491,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>```python
-if age &gt;= 18 and age &lt;= 65 and income &gt;= 15 and credit_score &gt;= 650:
-    print("Duyệt hồ sơ")
-```</t>
+          <t>Sử dụng đúng 4 khoảng trắng (4 spaces) cho mỗi cấp lồng nhau và tuyệt đối không trộn lẫn với phím Tab.</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -508,47 +505,35 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>```python
-if age &gt;= 18:
-    if age &lt;= 65:
-        if income &gt;= 15:
-            if credit_score &gt;= 650:
-                print("Duyệt hồ sơ")
-```</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
+          <t>Sử dụng đúng 2 khoảng trắng (2 spaces) cho mỗi cấp lồng nhau và có thể dùng phím Tab nếu thống nhất.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n"/>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>```python
-if age&gt;=18 and age&lt;=65 and income&gt;=15 and credit_score&gt;=650:
-  print("Duyệt hồ sơ")
-```</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr"/>
+          <t>Sử dụng phím Tab mặc định cho tất cả các khối lệnh lồng nhau để tối ưu hóa kích thước của tệp mã nguồn.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>```python
-if age &gt;= 18 or age &lt;= 65 or income &gt;= 15 or credit_score &gt;= 650:
-    print("Duyệt hồ sơ")
-```</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
+          <t>Sử dụng linh hoạt từ 2 đến 8 khoảng trắng miễn là các khối lệnh trong cùng một cấp thụt lề bằng nhau.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Một kỹ sư phần mềm thực hiện kiểm tra mã nguồn (Code Review) đối với khối lệnh rẽ nhánh trong hệ thống ngân hàng. Nguyên tắc định dạng nào dưới đây bắt buộc phải tuân thủ theo chuẩn PEP 8 của Python?</t>
+          <t>Trong hệ thống xét duyệt tín dụng, chương trình sử dụng cấu trúc `if` lồng nhau để kiểm tra độ tuổi và thu nhập. Cơ chế thực thi (Execution flow) của trình phiên dịch Python sẽ hoạt động như thế nào khi biểu thức điều kiện `if` ở tầng ngoài cùng đánh giá ra kết quả `False`?</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -556,17 +541,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Sử dụng phím Tab tự do để thụt lề và không sử dụng khoảng trắng xung quanh các toán tử so sánh.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
+          <t>Trình phiên dịch dừng chương trình và phát ra cảnh báo mâu thuẫn dữ liệu.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Sử dụng đúng 4 khoảng trắng cho mỗi cấp thụt lề và giữ khoảng trắng đơn xung quanh các toán tử so sánh cũng như toán tử logic.</t>
+          <t>Trình phiên dịch bỏ qua toàn bộ khối `if` lồng bên trong và chuyển xuống dưới.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -580,25 +565,41 @@
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Sử dụng 2 khoảng trắng cho mỗi cấp thụt lề và gộp tất cả biểu thức điều kiện vào một dòng không có khoảng cách.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr"/>
+          <t>Trình phiên dịch vẫn kiểm tra các điều kiện bên trong rồi mới đưa ra kết luận.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Sử dụng độ thụt lề linh hoạt tùy thuộc vào độ dài tên biến và không đặt khoảng trắng phía trước dấu hai chấm.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>Trình phiên dịch tạm lưu các điều kiện con vào RAM và chờ bổ sung thông tin.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Trường hợp nào dưới đây là ngữ cảnh hợp lý để sử dụng cấu trúc rẽ nhánh lồng nhau (Nested If) thay vì phẳng hóa điều kiện bằng toán tử logic?</t>
+          <t>Kỹ sư phần mềm chạy đoạn mã phân loại gói tín dụng cho một khách hàng cá nhân tại RikkeiBank với các thông số dữ liệu như sau:
+```python
+age = 25
+credit_score = 720
+monthly_income = 12
+status = "REJECTED"
+if age &gt;= 18:
+    if credit_score &gt;= 700:
+        if monthly_income &gt;= 15:
+            status = "APPROVED_HIGH"
+        else:
+            status = "APPROVED_STANDARD"
+    else:
+        status = "NEED_COLLATERAL"
+print(status)
+```python
+Giá trị của biến `status` được in ra màn hình sau khi đoạn mã trên kết thúc là gì?</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -606,27 +607,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Khi tất cả các điều kiện kiểm tra hoàn toàn độc lập và chỉ cần xác minh tính đúng đắn đồng thời.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
+          <t>"REJECTED"</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Khi lập trình viên muốn tạo hiệu ứng mã thụt lề dạng hình mũi tên để phân biệt các luồng xử lý.</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr"/>
+          <t>"APPROVED_HIGH"</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Khi điều kiện kiểm tra bên trong phụ thuộc vào kết quả xử lý hoặc giá trị trung gian được tính toán từ điều kiện bên ngoài.</t>
+          <t>"APPROVED_STANDARD"</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -640,19 +641,15 @@
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Khi hệ thống yêu cầu tối ưu hóa tốc độ bằng cách loại bỏ toán tử logic `and` khỏi câu lệnh điều kiện.</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr"/>
+          <t>"NEED_COLLATERAL"</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Giả sử hệ thống thẩm định nhận các tham số dữ liệu đầu vào: `age = 25`, `income = 10`, `credit_score = 700`. Khi chạy đoạn mã bên dưới, kết quả xử lý của chương trình sẽ ra sao?
-```python
-if age &gt;= 18 and income &gt;= 15 and credit_score &gt;= 650:
-    print("Hồ sơ đạt yêu cầu")
-```</t>
+          <t>Khi tái cấu trúc (refactoring) mã nguồn hệ thống thẩm định tín dụng, kỹ sư muốn thay thế một cấu trúc rẽ nhánh lồng sâu 4-5 tầng bằng cách sử dụng các câu lệnh kiểm tra điều kiện thoát sớm (Guard Clause). Điểm khác biệt quan trọng nhất về mặt thiết kế mã nguồn giữa hai cách tiếp cận này là gì?</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -660,37 +657,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>In ra chuỗi chữ 'Hồ sơ đạt yêu cầu' vì điều kiện tuổi và điểm tín dụng đã thỏa mãn.</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
+          <t>Cấu trúc lồng sâu bắt buộc Python phải biên dịch lại toàn bộ mã nguồn mỗi khi thực thi biểu thức rẽ nhánh.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Báo lỗi SyntaxError do toán tử `and` không thể kết hợp nhiều hơn hai biểu thức so sánh cùng lúc.</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr"/>
+          <t>Kỹ thuật Guard Clause giúp chương trình chiếm ít dung lượng RAM hơn hẳn so với việc lồng nhiều khối lệnh `if`.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Báo lỗi RuntimeError do khối lệnh rẽ nhánh thiếu câu lệnh xử lý trường hợp ngoại lệ.</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
+          <t>Cấu trúc lồng sâu đảm bảo tất cả các trường hợp ngoại lệ đều được hệ thống tự động xử lý mà không cần `else`.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Không in ra bất kỳ kết quả nào vì biểu thức `income &gt;= 15` trả về False, làm cho toàn bộ chuỗi điều kiện logic `and` nhận giá trị False.</t>
+          <t>Kỹ thuật Guard Clause thoát sớm khi điều kiện không thỏa mãn, giúp giảm độ sâu thụt lề và tránh mã vô hiệu.</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -698,6 +695,66 @@
           <t>TRUE</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Lập trình viên kiểm thử đoạn mã kiểm tra tài khoản định danh tại ngân hàng RikkeiBank với các câu lệnh điều kiện lồng nhau như sau:
+```python
+applicant_age = 22
+account_status = "PENDING"
+if applicant_age &gt;= 18:
+    account_status = "ELIGIBLE"
+    if applicant_age &lt; 18:
+        account_status = "UNDERAGE"
+print(account_status)
+```python
+Kết quả hiển thị ra màn hình khi chạy đoạn mã trên là gì?</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>"ELIGIBLE"</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>"UNDERAGE"</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>"PENDING"</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>IndentationError</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
